--- a/data/trans_orig/P1406-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1406-Estudios-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de úlcera de estómago en 2012</t>
+          <t>Población con diagnóstico de úlcera de estómago en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11561</t>
+          <t>11230</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28790</t>
+          <t>28737</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21562</t>
+          <t>21513</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43659</t>
+          <t>44268</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36758</t>
+          <t>36333</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>64429</t>
+          <t>64615</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>945853</t>
+          <t>945906</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>963082</t>
+          <t>963413</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1292955</t>
+          <t>1292346</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1315052</t>
+          <t>1315101</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2246828</t>
+          <t>2246642</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2274499</t>
+          <t>2274924</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,43%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11163</t>
+          <t>11815</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31098</t>
+          <t>31120</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3239</t>
+          <t>3258</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17903</t>
+          <t>17247</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18582</t>
+          <t>17550</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41328</t>
+          <t>41368</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1932859</t>
+          <t>1932837</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1952794</t>
+          <t>1952142</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1736689</t>
+          <t>1737345</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1751353</t>
+          <t>1751334</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3677221</t>
+          <t>3677181</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3699967</t>
+          <t>3700999</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,53%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>936</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8463</t>
+          <t>8343</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1019</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9751</t>
+          <t>10918</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3150</t>
+          <t>3145</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14744</t>
+          <t>15101</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>472718</t>
+          <t>472838</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>480227</t>
+          <t>480245</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>448880</t>
+          <t>447713</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>457612</t>
+          <t>457613</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>925069</t>
+          <t>924712</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>936663</t>
+          <t>936668</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,67%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29121</t>
+          <t>30056</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>54052</t>
+          <t>56055</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31032</t>
+          <t>30609</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59116</t>
+          <t>57587</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>64888</t>
+          <t>67920</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>104339</t>
+          <t>103974</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3365730</t>
+          <t>3363727</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3390661</t>
+          <t>3389726</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3490721</t>
+          <t>3492250</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3518805</t>
+          <t>3519228</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6865280</t>
+          <t>6865645</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6904731</t>
+          <t>6901699</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,03%</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de úlcera de estómago en 2016</t>
+          <t>Población con diagnóstico de úlcera de estómago en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2334,12 +2334,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1952</t>
+          <t>2169</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11935</t>
+          <t>11453</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2349,12 +2349,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9228</t>
+          <t>9427</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25370</t>
+          <t>27028</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2404,12 +2404,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13478</t>
+          <t>14070</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33617</t>
+          <t>33113</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2419,12 +2419,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>742412</t>
+          <t>742894</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>752395</t>
+          <t>752178</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>969290</t>
+          <t>967632</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>985432</t>
+          <t>985233</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1715390</t>
+          <t>1715894</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1735529</t>
+          <t>1734937</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,2%</t>
         </is>
       </c>
     </row>
@@ -2677,12 +2677,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3951</t>
+          <t>3733</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17215</t>
+          <t>17183</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8927</t>
+          <t>9165</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26250</t>
+          <t>26265</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -2747,12 +2747,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15444</t>
+          <t>16092</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35631</t>
+          <t>37086</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2762,12 +2762,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2059170</t>
+          <t>2059202</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2072434</t>
+          <t>2072652</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1962050</t>
+          <t>1962035</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1979373</t>
+          <t>1979135</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4029054</t>
+          <t>4027599</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4049241</t>
+          <t>4048593</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,6%</t>
         </is>
       </c>
     </row>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5083</t>
+          <t>4596</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3040,7 +3040,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6899</t>
+          <t>7379</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>904</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8642</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3110,7 +3110,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,69%</t>
         </is>
       </c>
     </row>
@@ -3133,7 +3133,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>541803</t>
+          <t>542290</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>542241</t>
+          <t>541761</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1087385</t>
+          <t>1088456</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1095119</t>
+          <t>1095123</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3218,7 +3218,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8327</t>
+          <t>8275</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25640</t>
+          <t>24622</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22688</t>
+          <t>23799</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47626</t>
+          <t>48373</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3413,12 +3413,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37010</t>
+          <t>37270</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>65371</t>
+          <t>64805</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3351978</t>
+          <t>3352996</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3369291</t>
+          <t>3369343</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3484474</t>
+          <t>3483727</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3509412</t>
+          <t>3508301</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6844347</t>
+          <t>6844913</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6872708</t>
+          <t>6872448</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">

--- a/data/trans_orig/P1406-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1406-Estudios-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11230</t>
+          <t>10717</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28737</t>
+          <t>27956</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21513</t>
+          <t>20975</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44268</t>
+          <t>45665</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36333</t>
+          <t>36743</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>64615</t>
+          <t>64783</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>945906</t>
+          <t>946687</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>963413</t>
+          <t>963926</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1292346</t>
+          <t>1290949</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1315101</t>
+          <t>1315639</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2246642</t>
+          <t>2246474</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2274924</t>
+          <t>2274514</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,41%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11815</t>
+          <t>12212</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31120</t>
+          <t>29841</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3258</t>
+          <t>3245</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17247</t>
+          <t>18481</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17550</t>
+          <t>17397</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41368</t>
+          <t>40502</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1932837</t>
+          <t>1934116</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1952142</t>
+          <t>1951745</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1737345</t>
+          <t>1736111</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1751334</t>
+          <t>1751347</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3677181</t>
+          <t>3678047</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3700999</t>
+          <t>3701152</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>947</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8343</t>
+          <t>8898</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1018</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10918</t>
+          <t>10110</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3145</t>
+          <t>3134</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15101</t>
+          <t>15185</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>472838</t>
+          <t>472283</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>480245</t>
+          <t>480234</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>447713</t>
+          <t>448521</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>457613</t>
+          <t>457598</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>924712</t>
+          <t>924628</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>936668</t>
+          <t>936679</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30056</t>
+          <t>28300</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56055</t>
+          <t>55869</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30609</t>
+          <t>31518</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>57587</t>
+          <t>59486</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>67920</t>
+          <t>64823</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>103974</t>
+          <t>103460</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3363727</t>
+          <t>3363913</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3389726</t>
+          <t>3391482</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3492250</t>
+          <t>3490351</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3519228</t>
+          <t>3518319</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6865645</t>
+          <t>6866159</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6901699</t>
+          <t>6904796</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -2334,12 +2334,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2169</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11453</t>
+          <t>12235</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2349,12 +2349,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9427</t>
+          <t>9078</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27028</t>
+          <t>26789</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2404,12 +2404,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14070</t>
+          <t>13318</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33113</t>
+          <t>33000</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>742894</t>
+          <t>742112</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>752178</t>
+          <t>752379</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>967632</t>
+          <t>967871</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>985233</t>
+          <t>985582</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1715894</t>
+          <t>1716007</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1734937</t>
+          <t>1735689</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,24%</t>
         </is>
       </c>
     </row>
@@ -2677,12 +2677,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3733</t>
+          <t>3638</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17183</t>
+          <t>17868</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9165</t>
+          <t>9401</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26265</t>
+          <t>26439</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2727,12 +2727,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2747,12 +2747,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16092</t>
+          <t>15986</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37086</t>
+          <t>36821</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2059202</t>
+          <t>2058517</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2072652</t>
+          <t>2072747</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1962035</t>
+          <t>1961861</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1979135</t>
+          <t>1978899</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4027599</t>
+          <t>4027864</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4048593</t>
+          <t>4048699</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,61%</t>
         </is>
       </c>
     </row>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4596</t>
+          <t>4273</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3040,7 +3040,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7379</t>
+          <t>6915</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>904</t>
+          <t>907</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7876</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3110,7 +3110,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -3133,7 +3133,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>542290</t>
+          <t>542613</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>541761</t>
+          <t>542225</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1088456</t>
+          <t>1088151</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1095123</t>
+          <t>1095120</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3218,7 +3218,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8275</t>
+          <t>8480</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24622</t>
+          <t>25764</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23799</t>
+          <t>23506</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48373</t>
+          <t>49016</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37270</t>
+          <t>36018</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>64805</t>
+          <t>64726</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3352996</t>
+          <t>3351854</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3369343</t>
+          <t>3369138</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3483727</t>
+          <t>3483084</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3508301</t>
+          <t>3508594</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6844913</t>
+          <t>6844992</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6872448</t>
+          <t>6873700</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
